--- a/49917_Intercuenca_49917/_raw_reportes_xlsx/IDConfig_11582_completo.xlsx
+++ b/49917_Intercuenca_49917/_raw_reportes_xlsx/IDConfig_11582_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re3b9619433e54f66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8035ce8846944de7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   5058.7900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   5303.9700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4926.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3931.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3626.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3595.1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3781.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4097.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4405.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49917_Intercuenca_49917/_raw_reportes_xlsx/IDConfig_11582_completo.xlsx
+++ b/49917_Intercuenca_49917/_raw_reportes_xlsx/IDConfig_11582_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8035ce8846944de7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5c5958481cf74326"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,696 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3890.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3916.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3959.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3860.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3602.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3529.5300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3734.5300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3919.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4038.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4011.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3982.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4177.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4367.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4426.0300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4342.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4443.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4700.2600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4548.8500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4771.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4838.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4585.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4194.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4182.7300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4399.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4669.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4684.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4180.3100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4601.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4788.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4500.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3806.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3627.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3588.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3384.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3346.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3277.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3283.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3311.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3366.0100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3467.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3682.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   3968.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4183.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4191.0800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4332.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   4618.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>   5058.7900</x:v>
+        <x:v>   5038.6600</x:v>
       </x:c>
     </x:row>
     <x:row>
